--- a/nr-rm-adeli/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-rm-adeli/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-06T10:53:29+00:00</t>
+    <t>2024-10-29T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension.where(url= 'https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.where(url = 'identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-core-1:If identityReliability status = 'VALI', then at least Patient.identifier[INS-NIR] or Patient.identifier[INS-NIA] or Patient.identifier[INS-NIR-TEST]or Patient.identifier[INS-NIR-DEMO] SHALL be present {(extension.where(url= 'https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-identity-reliability').extension.where(url = 'identityStatus').value.code = 'VALI') implies (identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.8').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.9').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.10').exists() or identifier.where(system = 'urn:oid:1.2.250.1.213.1.4.11').exists())}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>90</v>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>90</v>
@@ -9498,7 +9498,7 @@
         <v>385</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>432</v>
+        <v>386</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>387</v>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>90</v>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>90</v>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>90</v>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>90</v>
@@ -13586,7 +13586,7 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>90</v>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>90</v>
@@ -14643,7 +14643,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>90</v>
@@ -14881,7 +14881,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>90</v>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>90</v>
@@ -15938,7 +15938,7 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>90</v>
@@ -16757,7 +16757,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>90</v>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>90</v>
